--- a/raw-data/VFT Compiled data 2025/CM-25-all.xlsx
+++ b/raw-data/VFT Compiled data 2025/CM-25-all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\VFT Compiled data 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B5DB0-764F-4BCD-B549-0832CF5F766E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F46A6C1-037F-4398-B1E3-A9F6574048E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22943" yWindow="1365" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="250">
   <si>
     <t>ID</t>
   </si>
@@ -841,6 +841,10 @@
   </si>
   <si>
     <t>tp was yd, m25</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.20.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -7300,8 +7304,8 @@
       </c>
     </row>
     <row r="212" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="2">
-        <v>18.2</v>
+      <c r="A212" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="B212" s="2">
         <v>7</v>
